--- a/data/Excel/1.8.xlsx
+++ b/data/Excel/1.8.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oaa\Documents\GitHub\RAO_Project\data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SHARE_3.95\Templates_win_only\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8785EBE8-154E-4B47-AD6C-2DD7615252FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A46B10-2615-4104-BD38-ED0854EEA005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,12 +24,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
   <si>
     <t>Сведения об обособленном подразделении</t>
   </si>
@@ -71,42 +74,6 @@
   </si>
   <si>
     <t>Телефон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Должность, фамилия, имя, отчество (при наличии) руководителя -                                                                                                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Адрес обособленного подразделения -                                                                                                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сокращенное наименование обособленного подразделения (при наличии) -                                                                                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наименование обособленного подразделения -                                                                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Субъект Российской Федерации -                                                                                                                                                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Должность, фамилия, имя, отчество (при наличии) руководителя -       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Адрес  места осуществления деятельности юридического лица -      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Адрес юридического лица -          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сокращенное наименование юридического лица (при наличии)-   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наименование юридического лица -    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Субъект Российской Федерации - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Орган управления использованием атомной энергии -                                                                                                                                        </t>
   </si>
   <si>
     <t>2. Воинские части (организации) Вооруженных Сил Российской Федерации:
@@ -317,6 +284,36 @@
   </si>
   <si>
     <t>Договор</t>
+  </si>
+  <si>
+    <t>Орган управления использованием атомной энергии</t>
+  </si>
+  <si>
+    <t>Субъект Российской Федерации</t>
+  </si>
+  <si>
+    <t>Наименование юридического лица</t>
+  </si>
+  <si>
+    <t>Сокращенное наименование юридического лица (при наличии)</t>
+  </si>
+  <si>
+    <t>Адрес юридического лица</t>
+  </si>
+  <si>
+    <t>Адрес  места осуществления деятельности юридического лица</t>
+  </si>
+  <si>
+    <t>Должность, фамилия, имя, отчество (при наличии) руководителя</t>
+  </si>
+  <si>
+    <t>Наименование обособленного подразделения</t>
+  </si>
+  <si>
+    <t>Сокращенное наименование обособленного подразделения (при наличии)</t>
+  </si>
+  <si>
+    <t>Адрес обособленного подразделения</t>
   </si>
 </sst>
 </file>
@@ -545,19 +542,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1229,6 +1213,19 @@
       </top>
       <bottom style="medium">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1239,7 +1236,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1257,27 +1254,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1287,7 +1263,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -1300,9 +1276,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1318,41 +1291,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1362,35 +1304,141 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1398,9 +1446,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1410,55 +1455,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1470,55 +1500,64 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -1527,21 +1566,21 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1551,53 +1590,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1605,16 +1609,54 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1623,25 +1665,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1930,370 +1966,370 @@
   <dimension ref="A1:I37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="18" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="18" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="18" customWidth="1"/>
-    <col min="5" max="5" width="40.28515625" style="18" customWidth="1"/>
-    <col min="6" max="6" width="37.42578125" style="18" customWidth="1"/>
-    <col min="7" max="9" width="10.5703125" style="18" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="18"/>
+    <col min="1" max="1" width="16.7109375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="40.28515625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="37.42578125" style="11" customWidth="1"/>
+    <col min="7" max="9" width="10.5703125" style="11" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I1" s="19" t="s">
-        <v>35</v>
+      <c r="I1" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
+      <c r="A2" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
+      <c r="A3" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
     </row>
     <row r="4" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
+      <c r="A4" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
     </row>
     <row r="5" spans="1:9" ht="2.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
     </row>
     <row r="6" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="21"/>
-      <c r="E6" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23" t="s">
-        <v>30</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="27"/>
+      <c r="G6" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="56" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="59" t="s">
-        <v>27</v>
+      <c r="A10" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="65" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="59"/>
+      <c r="A11" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="65"/>
     </row>
     <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="59"/>
+      <c r="A12" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="65"/>
     </row>
     <row r="13" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="60"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="59"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="65"/>
     </row>
     <row r="14" spans="1:9" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="63"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="59"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="65"/>
     </row>
     <row r="15" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="53"/>
+      <c r="A15" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="59"/>
     </row>
     <row r="16" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="69" t="s">
+      <c r="A16" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="71" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="47"/>
+      <c r="B16" s="74" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="53"/>
     </row>
     <row r="17" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="69"/>
-      <c r="B17" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="47"/>
+      <c r="A17" s="73"/>
+      <c r="B17" s="75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="53"/>
     </row>
     <row r="18" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="69"/>
-      <c r="B18" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="47"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="53"/>
     </row>
     <row r="19" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="69"/>
-      <c r="B19" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="47"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="75" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="53"/>
     </row>
     <row r="20" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="69"/>
-      <c r="B20" s="73" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="47"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="75" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="53"/>
     </row>
     <row r="21" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="69"/>
-      <c r="B21" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="47"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="75" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
     </row>
     <row r="22" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="69"/>
-      <c r="B22" s="75" t="s">
+      <c r="A22" s="73"/>
+      <c r="B22" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
       <c r="E22" s="76"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="47"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="53"/>
     </row>
     <row r="23" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="69"/>
-      <c r="B23" s="75" t="s">
+      <c r="A23" s="73"/>
+      <c r="B23" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
       <c r="E23" s="76"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="53"/>
     </row>
     <row r="24" spans="1:9" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="70"/>
+      <c r="A24" s="73"/>
       <c r="B24" s="80" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="80"/>
       <c r="D24" s="80"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="50"/>
-    </row>
-    <row r="25" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="82" t="s">
+      <c r="E24" s="80"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="56"/>
+    </row>
+    <row r="25" spans="1:9" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="84" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="89"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="90"/>
-    </row>
-    <row r="26" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="69"/>
-      <c r="B26" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="92"/>
-    </row>
-    <row r="27" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="69"/>
-      <c r="B27" s="73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="92"/>
-    </row>
-    <row r="28" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="69"/>
-      <c r="B28" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="92"/>
-    </row>
-    <row r="29" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="69"/>
-      <c r="B29" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="91"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="92"/>
-    </row>
-    <row r="30" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="69"/>
-      <c r="B30" s="75" t="s">
+      <c r="B25" s="82" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="86"/>
+    </row>
+    <row r="26" spans="1:9" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="81"/>
+      <c r="B26" s="75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="88"/>
+      <c r="I26" s="89"/>
+    </row>
+    <row r="27" spans="1:9" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="81"/>
+      <c r="B27" s="75" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="89"/>
+    </row>
+    <row r="28" spans="1:9" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="81"/>
+      <c r="B28" s="75" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="88"/>
+      <c r="I28" s="89"/>
+    </row>
+    <row r="29" spans="1:9" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="81"/>
+      <c r="B29" s="75" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="75"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="89"/>
+    </row>
+    <row r="30" spans="1:9" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="81"/>
+      <c r="B30" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="75"/>
-      <c r="D30" s="75"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
       <c r="E30" s="76"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="47"/>
-    </row>
-    <row r="31" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="69"/>
-      <c r="B31" s="75" t="s">
+      <c r="F30" s="51"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53"/>
+    </row>
+    <row r="31" spans="1:9" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="81"/>
+      <c r="B31" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
       <c r="E31" s="76"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="47"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="53"/>
     </row>
     <row r="32" spans="1:9" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="83"/>
-      <c r="B32" s="86" t="s">
+      <c r="A32" s="81"/>
+      <c r="B32" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="50"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="56"/>
     </row>
     <row r="33" spans="1:9" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G33" s="24"/>
+      <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="77" t="s">
@@ -2309,34 +2345,34 @@
       <c r="I34" s="79"/>
     </row>
     <row r="35" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25"/>
-      <c r="B35" s="26" t="s">
+      <c r="A35" s="17"/>
+      <c r="B35" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="26" t="s">
+      <c r="E35" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="F35" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="26" t="s">
+      <c r="H35" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I35" s="26" t="s">
+      <c r="I35" s="18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="30" customFormat="1" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="27" t="s">
+    <row r="36" spans="1:9" s="20" customFormat="1" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="19" t="s">
         <v>1</v>
       </c>
       <c r="B36" s="28"/>
@@ -2348,20 +2384,21 @@
       <c r="H36" s="29"/>
       <c r="I36" s="29"/>
     </row>
-    <row r="37" spans="1:9" s="30" customFormat="1" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="31" t="s">
+    <row r="37" spans="1:9" s="20" customFormat="1" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="25"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="9R9PYYU2WaSTZKyIpPww5yTg+zHA+ApIww5R7S7dLK9XoNMnxWSbrDrP/kv0ZSZN1WeghFDcmCnqGI0Ax6LVwg==" saltValue="iwXv/s6BzTal1YMwkDz8Gg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="46">
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="B24:E24"/>
@@ -2434,53 +2471,53 @@
       <c r="E1" s="1"/>
       <c r="AB1" s="3"/>
       <c r="AC1" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="97"/>
-      <c r="R2" s="97"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
-      <c r="V2" s="97"/>
-      <c r="W2" s="97"/>
-      <c r="X2" s="97"/>
-      <c r="Y2" s="97"/>
-      <c r="Z2" s="97"/>
-      <c r="AA2" s="97"/>
-      <c r="AB2" s="97"/>
-      <c r="AC2" s="97"/>
+      <c r="A2" s="98" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
+      <c r="Q2" s="98"/>
+      <c r="R2" s="98"/>
+      <c r="S2" s="98"/>
+      <c r="T2" s="98"/>
+      <c r="U2" s="98"/>
+      <c r="V2" s="98"/>
+      <c r="W2" s="98"/>
+      <c r="X2" s="98"/>
+      <c r="Y2" s="98"/>
+      <c r="Z2" s="98"/>
+      <c r="AA2" s="98"/>
+      <c r="AB2" s="98"/>
+      <c r="AC2" s="98"/>
     </row>
     <row r="3" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="98" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
+      <c r="A3" s="99" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -2504,16 +2541,16 @@
       <c r="AC3" s="4"/>
     </row>
     <row r="4" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="98" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
+      <c r="A4" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -2537,191 +2574,191 @@
       <c r="AC4" s="4"/>
     </row>
     <row r="5" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="98" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
+      <c r="A5" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
     </row>
     <row r="6" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="103" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="104"/>
+      <c r="D7" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="105" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="106"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="105" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="107"/>
+      <c r="P7" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="105" t="s">
+        <v>33</v>
+      </c>
+      <c r="S7" s="106"/>
+      <c r="T7" s="106"/>
+      <c r="U7" s="106"/>
+      <c r="V7" s="106"/>
+      <c r="W7" s="106"/>
+      <c r="X7" s="106"/>
+      <c r="Y7" s="106"/>
+      <c r="Z7" s="106"/>
+      <c r="AA7" s="108" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB7" s="126" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC7" s="129" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD7" s="5"/>
+    </row>
+    <row r="8" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="101"/>
+      <c r="B8" s="90" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="96" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="96" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="102" t="s">
+      <c r="G8" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="104" t="s">
+      <c r="H8" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="104" t="s">
+      <c r="I8" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="105"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="106"/>
-      <c r="P7" s="104" t="s">
+      <c r="J8" s="107"/>
+      <c r="K8" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="Q7" s="106"/>
-      <c r="R7" s="104" t="s">
+      <c r="L8" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="S7" s="105"/>
-      <c r="T7" s="105"/>
-      <c r="U7" s="105"/>
-      <c r="V7" s="105"/>
-      <c r="W7" s="105"/>
-      <c r="X7" s="105"/>
-      <c r="Y7" s="105"/>
-      <c r="Z7" s="105"/>
-      <c r="AA7" s="132" t="s">
+      <c r="M8" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="AB7" s="129" t="s">
+      <c r="O8" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="AC7" s="135" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD7" s="5"/>
-    </row>
-    <row r="8" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="100"/>
-      <c r="B8" s="109" t="s">
+      <c r="P8" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="95" t="s">
+      <c r="Q8" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="95" t="s">
+      <c r="R8" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="95" t="s">
+      <c r="S8" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="95" t="s">
+      <c r="T8" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="95" t="s">
+      <c r="U8" s="133" t="s">
+        <v>41</v>
+      </c>
+      <c r="V8" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="111" t="s">
+      <c r="W8" s="106"/>
+      <c r="X8" s="106"/>
+      <c r="Y8" s="107"/>
+      <c r="Z8" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="104" t="s">
+      <c r="AA8" s="109"/>
+      <c r="AB8" s="127"/>
+      <c r="AC8" s="130"/>
+      <c r="AD8" s="10"/>
+    </row>
+    <row r="9" spans="1:30" ht="320.10000000000002" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="102"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="106"/>
-      <c r="K8" s="107" t="s">
+      <c r="J9" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="95" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="95" t="s">
-        <v>49</v>
-      </c>
-      <c r="N8" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" s="95" t="s">
-        <v>59</v>
-      </c>
-      <c r="P8" s="95" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q8" s="107" t="s">
-        <v>61</v>
-      </c>
-      <c r="R8" s="107" t="s">
-        <v>62</v>
-      </c>
-      <c r="S8" s="93" t="s">
-        <v>63</v>
-      </c>
-      <c r="T8" s="95" t="s">
-        <v>64</v>
-      </c>
-      <c r="U8" s="111" t="s">
-        <v>53</v>
-      </c>
-      <c r="V8" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="W8" s="105"/>
-      <c r="X8" s="105"/>
-      <c r="Y8" s="106"/>
-      <c r="Z8" s="127" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA8" s="133"/>
-      <c r="AB8" s="130"/>
-      <c r="AC8" s="136"/>
-      <c r="AD8" s="17"/>
-    </row>
-    <row r="9" spans="1:30" ht="320.10000000000002" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="101"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="6" t="s">
+      <c r="K9" s="93"/>
+      <c r="L9" s="97"/>
+      <c r="M9" s="97"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="97"/>
+      <c r="P9" s="97"/>
+      <c r="Q9" s="93"/>
+      <c r="R9" s="93"/>
+      <c r="S9" s="95"/>
+      <c r="T9" s="97"/>
+      <c r="U9" s="97"/>
+      <c r="V9" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="W9" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="108"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="108"/>
-      <c r="S9" s="94"/>
-      <c r="T9" s="96"/>
-      <c r="U9" s="96"/>
-      <c r="V9" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="W9" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="X9" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y9" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z9" s="128"/>
-      <c r="AA9" s="134"/>
-      <c r="AB9" s="131"/>
-      <c r="AC9" s="137" t="s">
-        <v>57</v>
+      <c r="X9" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y9" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z9" s="132"/>
+      <c r="AA9" s="110"/>
+      <c r="AB9" s="128"/>
+      <c r="AC9" s="26" t="s">
+        <v>45</v>
       </c>
       <c r="AD9" s="5"/>
     </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="32">
         <v>1</v>
       </c>
@@ -2731,215 +2768,224 @@
       <c r="C10" s="32">
         <v>3</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>4</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="34">
         <v>5</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="35">
         <v>6</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="36">
         <v>7</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="35">
         <v>8</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="37">
         <v>9</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="38">
         <v>10</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="38">
         <v>11</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="38">
         <v>12</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="38">
         <v>13</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="38">
         <v>14</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="38">
         <v>15</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="38">
         <v>16</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="38">
         <v>17</v>
       </c>
-      <c r="R10" s="10">
+      <c r="R10" s="38">
         <v>18</v>
       </c>
-      <c r="S10" s="10">
+      <c r="S10" s="38">
         <v>19</v>
       </c>
-      <c r="T10" s="10">
+      <c r="T10" s="38">
         <v>20</v>
       </c>
-      <c r="U10" s="11">
+      <c r="U10" s="39">
         <v>21</v>
       </c>
-      <c r="V10" s="10">
+      <c r="V10" s="38">
         <v>22</v>
       </c>
-      <c r="W10" s="10">
+      <c r="W10" s="38">
         <v>23</v>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="40">
         <v>24</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="Y10" s="41">
         <v>25</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="42">
         <v>26</v>
       </c>
-      <c r="AA10" s="38">
+      <c r="AA10" s="43">
         <v>27</v>
       </c>
-      <c r="AB10" s="39">
+      <c r="AB10" s="44">
         <v>28</v>
       </c>
-      <c r="AC10" s="39">
+      <c r="AC10" s="44">
         <v>29</v>
       </c>
-      <c r="AD10" s="5"/>
-    </row>
-    <row r="11" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="33"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="33"/>
-      <c r="Z11" s="33"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="33"/>
-    </row>
+      <c r="AD10" s="45"/>
+    </row>
+    <row r="11" spans="1:30" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="47"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="47"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="47"/>
+      <c r="V11" s="47"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="47"/>
+      <c r="Y11" s="47"/>
+      <c r="Z11" s="47"/>
+      <c r="AA11" s="47"/>
+      <c r="AB11" s="47"/>
+      <c r="AC11" s="47"/>
+    </row>
+    <row r="12" spans="1:30" s="46" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-    </row>
-    <row r="14" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="114" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="115"/>
-      <c r="C14" s="114" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="115"/>
-      <c r="E14" s="116" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="118"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-    </row>
-    <row r="15" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="119"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="122"/>
-      <c r="O15" s="14"/>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="O16" s="14"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+    </row>
+    <row r="14" spans="1:30" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="116"/>
+      <c r="C14" s="115" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="116"/>
+      <c r="E14" s="117" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="119"/>
+      <c r="N14" s="49"/>
+      <c r="O14" s="49"/>
+    </row>
+    <row r="15" spans="1:30" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="120"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="123"/>
+      <c r="O15" s="49"/>
+    </row>
+    <row r="16" spans="1:30" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O16" s="49"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="112" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="112"/>
-      <c r="C18" s="112"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="113"/>
-      <c r="L18" s="113"/>
+      <c r="A18" s="114" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="114"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="111"/>
     </row>
     <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="43"/>
-      <c r="F19" s="123" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="123"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="J19" s="42"/>
-      <c r="K19" s="124" t="s">
-        <v>77</v>
-      </c>
-      <c r="L19" s="124"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="24"/>
+      <c r="F19" s="112" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="112"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="23"/>
+      <c r="K19" s="113" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="113"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="IBfNCf0Ge/ngqE7VXV/w8o4CwpYqGzi+EiTiWfDW2wTuPqklrKryDQQfCHO4lT599vyHuvT6DrHbqUuCDc6K7Q==" saltValue="Nc2UFpYlvviYCiNGz9Lz2A==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" insertRows="0"/>
   <mergeCells count="49">
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="AB7:AB9"/>
     <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
@@ -2953,24 +2999,9 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:J15"/>
-    <mergeCell ref="V8:Y8"/>
-    <mergeCell ref="Z8:Z9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
     <mergeCell ref="A2:AC2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
@@ -2983,7 +3014,15 @@
     <mergeCell ref="P7:Q7"/>
     <mergeCell ref="R7:Z7"/>
     <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="AB7:AB9"/>
     <mergeCell ref="B8:B9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="49" fitToHeight="1000" orientation="landscape" r:id="rId1"/>
